--- a/data/trans_orig/cron_prev_index-Edad-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Índice de cronicidad física en base a la prevalencia</t>
+          <t>Índice de cronicidad física en base a la prevalencia (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,7 +731,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,28</t>
+          <t>0,13; 0,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,17 +741,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,18</t>
+          <t>0,1; 0,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,19</t>
+          <t>0,12; 0,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,25</t>
+          <t>0,12; 0,26</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,18</t>
+          <t>0,12; 0,17</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,25</t>
+          <t>0,14; 0,24</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,18</t>
+          <t>0,11; 0,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,27</t>
+          <t>0,15; 0,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,19</t>
+          <t>0,13; 0,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,57</t>
+          <t>0,2; 0,58</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,22</t>
+          <t>0,14; 0,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 0,26</t>
+          <t>0,17; 0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,31</t>
+          <t>0,22; 0,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,31</t>
+          <t>0,24; 0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,27</t>
+          <t>0,2; 0,27</t>
         </is>
       </c>
     </row>
@@ -1146,7 +1146,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,47</t>
+          <t>0,36; 0,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1161,17 +1161,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,41; 0,54</t>
+          <t>0,41; 0,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 0,49</t>
+          <t>0,36; 0,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,61</t>
+          <t>0,46; 0,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,44</t>
+          <t>0,36; 0,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,57</t>
+          <t>0,3; 0,58</t>
         </is>
       </c>
     </row>
@@ -1276,42 +1276,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 1,03</t>
+          <t>0,85; 1,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 0,99</t>
+          <t>0,8; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,9</t>
+          <t>0,69; 0,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,05</t>
+          <t>0,87; 1,04</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 1,15</t>
+          <t>0,95; 1,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,22</t>
+          <t>1,0; 1,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 1,08</t>
+          <t>0,89; 1,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,03</t>
+          <t>0,89; 1,04</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 0,97</t>
+          <t>0,82; 0,96</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1416,42 +1416,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,07; 1,32</t>
+          <t>1,08; 1,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,45; 1,75</t>
+          <t>1,46; 1,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,43</t>
+          <t>1,19; 1,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,4</t>
+          <t>1,2; 1,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,76</t>
+          <t>1,5; 1,74</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 1,81</t>
+          <t>1,55; 1,8</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,35; 1,61</t>
+          <t>1,37; 1,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,58</t>
+          <t>1,46; 2,54</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,73</t>
+          <t>1,55; 1,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,31</t>
+          <t>1,38; 2,35</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,64</t>
+          <t>1,34; 1,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,67; 1,99</t>
+          <t>1,68; 2,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 1,78</t>
+          <t>1,54; 1,79</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,87</t>
+          <t>1,62; 1,88</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 1,96</t>
+          <t>1,71; 1,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,19</t>
+          <t>1,92; 2,19</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 1,93</t>
+          <t>1,64; 1,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 2,21</t>
+          <t>2,02; 2,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,6; 1,8</t>
+          <t>1,61; 1,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,07</t>
+          <t>1,89; 2,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,83</t>
+          <t>1,63; 1,83</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,04</t>
+          <t>1,89; 2,05</t>
         </is>
       </c>
     </row>
@@ -1711,32 +1711,32 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 0,69</t>
+          <t>0,49; 0,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>0,62; 0,68</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,67; 0,74</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>0,62; 0,69</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,67; 0,75</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,62; 0,69</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 1,3</t>
+          <t>0,78; 1,29</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0,53; 0,57</t>
+          <t>0,53; 0,58</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1751,7 +1751,7 @@
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,0</t>
+          <t>0,69; 0,98</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/cron_prev_index-Edad-trans_orig.xlsx
+++ b/data/trans_orig/cron_prev_index-Edad-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,2</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,18</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>0,18</t>
         </is>
       </c>
     </row>
@@ -726,12 +726,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 0,18</t>
+          <t>0,11; 0,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,3</t>
+          <t>0,12; 0,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,2</t>
+          <t>0,12; 0,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,26</t>
+          <t>0,12; 0,25</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,14</t>
+          <t>0,1; 0,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,17</t>
+          <t>0,13; 0,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,24</t>
+          <t>0,13; 0,22</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,31</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,2</t>
         </is>
       </c>
     </row>
@@ -876,22 +876,22 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,2</t>
+          <t>0,13; 0,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 0,2</t>
+          <t>0,13; 0,21</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,19</t>
+          <t>0,13; 0,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,58</t>
+          <t>0,16; 0,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -906,12 +906,12 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,16</t>
+          <t>0,12; 0,17</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,44</t>
+          <t>0,17; 0,24</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,21</t>
+          <t>0,24</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,25</t>
         </is>
       </c>
     </row>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 0,26</t>
+          <t>0,18; 0,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,31</t>
+          <t>0,23; 0,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 0,25</t>
+          <t>0,21; 0,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 0,27</t>
+          <t>0,22; 0,28</t>
         </is>
       </c>
     </row>
@@ -1083,47 +1083,47 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
+          <t>0,57</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,47</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0,43</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>0,55</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,46</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
           <t>0,42</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,47</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,43</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,54</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,46</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>0,56</t>
         </is>
       </c>
     </row>
@@ -1136,22 +1136,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,49</t>
+          <t>0,35; 0,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,39</t>
+          <t>0,29; 0,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,48</t>
+          <t>0,36; 0,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,19; 0,61</t>
+          <t>0,5; 0,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 0,48</t>
+          <t>0,37; 0,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 0,62</t>
+          <t>0,5; 0,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,3; 0,58</t>
+          <t>0,51; 0,6</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,95</t>
+          <t>0,93</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,96</t>
+          <t>0,97</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1276,22 +1276,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,05</t>
+          <t>0,83; 1,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,8; 1,0</t>
+          <t>0,79; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,89</t>
+          <t>0,69; 0,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,04</t>
+          <t>0,85; 1,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 1,22</t>
+          <t>1,01; 1,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 1,04</t>
+          <t>0,9; 1,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 1,08</t>
+          <t>0,92; 1,07</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 1,01</t>
+          <t>0,9; 1,0</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,3</t>
+          <t>1,27</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,0</t>
+          <t>1,51</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,73</t>
+          <t>1,39</t>
         </is>
       </c>
     </row>
@@ -1416,47 +1416,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,08; 1,31</t>
+          <t>1,07; 1,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 1,76</t>
+          <t>1,45; 1,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,19; 1,42</t>
+          <t>1,19; 1,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 1,4</t>
+          <t>1,16; 1,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 1,74</t>
+          <t>1,5; 1,75</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 1,8</t>
+          <t>1,56; 1,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,37; 1,62</t>
+          <t>1,35; 1,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,54</t>
+          <t>1,42; 1,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,34; 1,51</t>
+          <t>1,33; 1,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,38; 2,35</t>
+          <t>1,33; 1,46</t>
         </is>
       </c>
     </row>
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,12</t>
+          <t>2,1</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>1,96</t>
         </is>
       </c>
     </row>
@@ -1561,27 +1561,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,01</t>
+          <t>1,66; 1,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 1,79</t>
+          <t>1,53; 1,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 1,88</t>
+          <t>1,62; 1,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 1,98</t>
+          <t>1,7; 1,97</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,92; 2,19</t>
+          <t>1,94; 2,2</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1591,17 +1591,17 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,22</t>
+          <t>2,0; 2,2</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,61; 1,81</t>
+          <t>1,6; 1,8</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,07</t>
+          <t>1,87; 2,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,05</t>
+          <t>1,88; 2,04</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0,91</t>
+          <t>0,79</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,77</t>
+          <t>0,73</t>
         </is>
       </c>
     </row>
@@ -1711,12 +1711,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,49; 0,69</t>
+          <t>0,63; 0,7</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 0,68</t>
+          <t>0,62; 0,69</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,78; 1,29</t>
+          <t>0,76; 0,82</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1746,12 +1746,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,56; 0,61</t>
+          <t>0,57; 0,61</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 0,98</t>
+          <t>0,71; 0,75</t>
         </is>
       </c>
     </row>
